--- a/erp-server/erp-server-wms/src/main/resources/excel/qcBillExport.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/qcBillExport.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -62,16 +62,16 @@
     <t>SKU名称</t>
   </si>
   <si>
-    <t>总数量</t>
-  </si>
-  <si>
-    <t>质检量</t>
-  </si>
-  <si>
-    <t>质检合格量</t>
-  </si>
-  <si>
-    <t>质检不良量</t>
+    <t>送检数量</t>
+  </si>
+  <si>
+    <t>抽检数量</t>
+  </si>
+  <si>
+    <t>抽检良品数量</t>
+  </si>
+  <si>
+    <t>抽检不良品数量</t>
   </si>
   <si>
     <t>检验结果</t>
@@ -684,7 +684,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
